--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.75998711816006</v>
+        <v>6.94849790670101</v>
       </c>
       <c r="D2" t="n">
-        <v>42.45197793479568</v>
+        <v>6.898446414404298</v>
       </c>
       <c r="E2" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F2" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.33861079707252</v>
+        <v>6.717524254524284</v>
       </c>
       <c r="D3" t="n">
-        <v>40.70268495661998</v>
+        <v>6.614186305450747</v>
       </c>
       <c r="E3" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F3" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.05584073044607</v>
+        <v>5.696574118697487</v>
       </c>
       <c r="D4" t="n">
-        <v>34.59756095464868</v>
+        <v>5.62210365513041</v>
       </c>
       <c r="E4" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F4" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.98614554302833</v>
+        <v>6.497748650742103</v>
       </c>
       <c r="D5" t="n">
-        <v>39.82451644488371</v>
+        <v>6.471483922293603</v>
       </c>
       <c r="E5" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F5" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.71481849584894</v>
+        <v>6.291158005575452</v>
       </c>
       <c r="D6" t="n">
-        <v>38.08076006839698</v>
+        <v>6.18812351111451</v>
       </c>
       <c r="E6" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F6" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28221592455468</v>
+        <v>2.645860087740135</v>
       </c>
       <c r="D7" t="n">
-        <v>15.64293575774679</v>
+        <v>2.541977060633853</v>
       </c>
       <c r="E7" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F7" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.11460126217913</v>
+        <v>3.593622705104109</v>
       </c>
       <c r="D8" t="n">
-        <v>22.21546501109589</v>
+        <v>3.610013064303083</v>
       </c>
       <c r="E8" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F8" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.21387594628076</v>
+        <v>6.047254841270624</v>
       </c>
       <c r="D9" t="n">
-        <v>37.42592673001167</v>
+        <v>6.081713093626897</v>
       </c>
       <c r="E9" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F9" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71459761454048</v>
+        <v>6.616122112362828</v>
       </c>
       <c r="D10" t="n">
-        <v>40.32060868649542</v>
+        <v>6.552098911555506</v>
       </c>
       <c r="E10" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F10" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.61973702743147</v>
+        <v>5.625707266957614</v>
       </c>
       <c r="D11" t="n">
-        <v>35.07267739429874</v>
+        <v>5.699310076573546</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F11" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.617642891769909</v>
+        <v>1.23786696991261</v>
       </c>
       <c r="D12" t="n">
-        <v>8.113314026900669</v>
+        <v>1.318413529371359</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F12" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.44894179284622</v>
+        <v>3.810453041337511</v>
       </c>
       <c r="D13" t="n">
-        <v>24.08922582773639</v>
+        <v>3.914499197007163</v>
       </c>
       <c r="E13" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F13" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.09378165090143</v>
+        <v>4.240239518271482</v>
       </c>
       <c r="D14" t="n">
-        <v>26.6513947833963</v>
+        <v>4.3308516523019</v>
       </c>
       <c r="E14" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F14" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.61935812050706</v>
+        <v>6.275645694582397</v>
       </c>
       <c r="D15" t="n">
-        <v>38.78181150250049</v>
+        <v>6.30204436915633</v>
       </c>
       <c r="E15" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F15" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.17611866970879</v>
+        <v>6.528619283827679</v>
       </c>
       <c r="D16" t="n">
-        <v>40.81578338723989</v>
+        <v>6.632564800426482</v>
       </c>
       <c r="E16" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F16" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.01474678582841</v>
+        <v>6.177396352697118</v>
       </c>
       <c r="D17" t="n">
-        <v>38.46077649023908</v>
+        <v>6.249876179663851</v>
       </c>
       <c r="E17" t="n">
-        <v>10.05624321841102</v>
+        <v>1.634139522991791</v>
       </c>
       <c r="F17" t="n">
-        <v>9.939314690808986</v>
+        <v>1.61513863725646</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
